--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92536483409</v>
+        <v>46157.93109777688</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93109777688</v>
+        <v>46157.93365331821</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93365331821</v>
+        <v>46157.93667158927</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93667158927</v>
+        <v>46158.28191893979</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28191893979</v>
+        <v>46158.29712423145</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29712423145</v>
+        <v>46158.29786874481</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29786874481</v>
+        <v>46158.33352673881</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33352673881</v>
+        <v>46158.37209186322</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37209186322</v>
+        <v>46158.37426755124</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
